--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486418</v>
+        <v>128486465</v>
       </c>
       <c r="B2" t="n">
-        <v>86823</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558889</v>
+        <v>558900</v>
       </c>
       <c r="R2" t="n">
-        <v>6680512</v>
+        <v>6680527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486598</v>
+        <v>128486559</v>
       </c>
       <c r="B3" t="n">
-        <v>86823</v>
+        <v>92776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558837</v>
+        <v>558846</v>
       </c>
       <c r="R3" t="n">
-        <v>6680592</v>
+        <v>6680607</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,6 +866,1655 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128486359</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92744</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>788</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6680514</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128486263</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558915</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6680423</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128486823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558883</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6680540</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128486429</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558884</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6680516</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128486876</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558954</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6680549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128486567</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558829</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6680608</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128486873</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558945</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6680547</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128486924</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6680658</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128486418</v>
+      </c>
+      <c r="B12" t="n">
+        <v>86915</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6680512</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128486630</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558850</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6680597</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128486971</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6680596</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128486655</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558858</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6680578</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128486310</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558879</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6680448</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128486727</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558855</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6680550</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128486598</v>
+      </c>
+      <c r="B18" t="n">
+        <v>86915</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558837</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6680592</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128486938</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>558925</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6680676</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128486478</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>558870</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6680544</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486465</v>
+        <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558900</v>
+        <v>558865</v>
       </c>
       <c r="R2" t="n">
-        <v>6680527</v>
+        <v>6680514</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B4" t="n">
-        <v>92744</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R4" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486429</v>
+        <v>128486567</v>
       </c>
       <c r="B7" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558884</v>
+        <v>558829</v>
       </c>
       <c r="R7" t="n">
-        <v>6680516</v>
+        <v>6680608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486567</v>
+        <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558829</v>
+        <v>558884</v>
       </c>
       <c r="R9" t="n">
-        <v>6680608</v>
+        <v>6680516</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B11" t="n">
-        <v>92776</v>
+        <v>86915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R11" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B12" t="n">
-        <v>86915</v>
+        <v>92776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R12" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486971</v>
+        <v>128486310</v>
       </c>
       <c r="B14" t="n">
-        <v>92776</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558970</v>
+        <v>558879</v>
       </c>
       <c r="R14" t="n">
-        <v>6680596</v>
+        <v>6680448</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486310</v>
+        <v>128486971</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558879</v>
+        <v>558970</v>
       </c>
       <c r="R16" t="n">
-        <v>6680448</v>
+        <v>6680596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128486598</v>
+        <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>86915</v>
+        <v>92776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558837</v>
+        <v>558870</v>
       </c>
       <c r="R18" t="n">
-        <v>6680592</v>
+        <v>6680544</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2421,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128486478</v>
+        <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>92776</v>
+        <v>86915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558870</v>
+        <v>558837</v>
       </c>
       <c r="R20" t="n">
-        <v>6680544</v>
+        <v>6680592</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B2" t="n">
-        <v>92744</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R2" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486559</v>
+        <v>128486359</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>92744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558846</v>
+        <v>558865</v>
       </c>
       <c r="R3" t="n">
-        <v>6680607</v>
+        <v>6680514</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486465</v>
+        <v>128486559</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558900</v>
+        <v>558846</v>
       </c>
       <c r="R4" t="n">
-        <v>6680527</v>
+        <v>6680607</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486567</v>
+        <v>128486876</v>
       </c>
       <c r="B7" t="n">
         <v>92387</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558829</v>
+        <v>558954</v>
       </c>
       <c r="R7" t="n">
-        <v>6680608</v>
+        <v>6680549</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486876</v>
+        <v>128486429</v>
       </c>
       <c r="B8" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558954</v>
+        <v>558884</v>
       </c>
       <c r="R8" t="n">
-        <v>6680549</v>
+        <v>6680516</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486429</v>
+        <v>128486567</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558884</v>
+        <v>558829</v>
       </c>
       <c r="R9" t="n">
-        <v>6680516</v>
+        <v>6680608</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486310</v>
+        <v>128486655</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558879</v>
+        <v>558858</v>
       </c>
       <c r="R14" t="n">
-        <v>6680448</v>
+        <v>6680578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486655</v>
+        <v>128486971</v>
       </c>
       <c r="B15" t="n">
         <v>92776</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558858</v>
+        <v>558970</v>
       </c>
       <c r="R15" t="n">
-        <v>6680578</v>
+        <v>6680596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486971</v>
+        <v>128486310</v>
       </c>
       <c r="B16" t="n">
-        <v>92776</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558970</v>
+        <v>558879</v>
       </c>
       <c r="R16" t="n">
-        <v>6680596</v>
+        <v>6680448</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486465</v>
+        <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558900</v>
+        <v>558865</v>
       </c>
       <c r="R2" t="n">
-        <v>6680527</v>
+        <v>6680514</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B3" t="n">
-        <v>92744</v>
+        <v>92393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R3" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>128486559</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486876</v>
+        <v>128486567</v>
       </c>
       <c r="B7" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558954</v>
+        <v>558829</v>
       </c>
       <c r="R7" t="n">
-        <v>6680549</v>
+        <v>6680608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486429</v>
+        <v>128486876</v>
       </c>
       <c r="B8" t="n">
-        <v>92776</v>
+        <v>92393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558884</v>
+        <v>558954</v>
       </c>
       <c r="R8" t="n">
-        <v>6680516</v>
+        <v>6680549</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486567</v>
+        <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558829</v>
+        <v>558884</v>
       </c>
       <c r="R9" t="n">
-        <v>6680608</v>
+        <v>6680516</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>86915</v>
+        <v>92782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R11" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>92776</v>
+        <v>86919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R12" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128486655</v>
       </c>
       <c r="B14" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128486971</v>
       </c>
       <c r="B15" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128486310</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>86915</v>
+        <v>86919</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486465</v>
+        <v>128486559</v>
       </c>
       <c r="B3" t="n">
-        <v>92393</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558900</v>
+        <v>558846</v>
       </c>
       <c r="R3" t="n">
-        <v>6680527</v>
+        <v>6680607</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486559</v>
+        <v>128486465</v>
       </c>
       <c r="B4" t="n">
-        <v>92782</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558846</v>
+        <v>558900</v>
       </c>
       <c r="R4" t="n">
-        <v>6680607</v>
+        <v>6680527</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128486567</v>
       </c>
       <c r="B7" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128486876</v>
       </c>
       <c r="B8" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>86919</v>
+        <v>86925</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128486655</v>
       </c>
       <c r="B14" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128486971</v>
       </c>
       <c r="B15" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128486310</v>
       </c>
       <c r="B16" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>90993</v>
+        <v>90999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>86919</v>
+        <v>86925</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R2" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486465</v>
+        <v>128486359</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558900</v>
+        <v>558865</v>
       </c>
       <c r="R4" t="n">
-        <v>6680527</v>
+        <v>6680514</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128486465</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486559</v>
+        <v>128486359</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558846</v>
+        <v>558865</v>
       </c>
       <c r="R3" t="n">
-        <v>6680607</v>
+        <v>6680514</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486359</v>
+        <v>128486559</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558865</v>
+        <v>558846</v>
       </c>
       <c r="R4" t="n">
-        <v>6680514</v>
+        <v>6680607</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486567</v>
+        <v>128486429</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558829</v>
+        <v>558884</v>
       </c>
       <c r="R7" t="n">
-        <v>6680608</v>
+        <v>6680516</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486876</v>
+        <v>128486567</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558954</v>
+        <v>558829</v>
       </c>
       <c r="R8" t="n">
-        <v>6680549</v>
+        <v>6680608</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486429</v>
+        <v>128486876</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558884</v>
+        <v>558954</v>
       </c>
       <c r="R9" t="n">
-        <v>6680516</v>
+        <v>6680549</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B11" t="n">
-        <v>92788</v>
+        <v>86927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R11" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B12" t="n">
-        <v>86925</v>
+        <v>92790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R12" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486655</v>
+        <v>128486310</v>
       </c>
       <c r="B14" t="n">
-        <v>92788</v>
+        <v>92768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558858</v>
+        <v>558879</v>
       </c>
       <c r="R14" t="n">
-        <v>6680578</v>
+        <v>6680448</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486971</v>
+        <v>128486655</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558970</v>
+        <v>558858</v>
       </c>
       <c r="R15" t="n">
-        <v>6680596</v>
+        <v>6680578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486310</v>
+        <v>128486971</v>
       </c>
       <c r="B16" t="n">
-        <v>92766</v>
+        <v>92790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558879</v>
+        <v>558970</v>
       </c>
       <c r="R16" t="n">
-        <v>6680448</v>
+        <v>6680596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486465</v>
+        <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558900</v>
+        <v>558865</v>
       </c>
       <c r="R2" t="n">
-        <v>6680527</v>
+        <v>6680514</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486359</v>
+        <v>128486559</v>
       </c>
       <c r="B3" t="n">
-        <v>92758</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558865</v>
+        <v>558846</v>
       </c>
       <c r="R3" t="n">
-        <v>6680514</v>
+        <v>6680607</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486559</v>
+        <v>128486465</v>
       </c>
       <c r="B4" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558846</v>
+        <v>558900</v>
       </c>
       <c r="R4" t="n">
-        <v>6680607</v>
+        <v>6680527</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486429</v>
+        <v>128486567</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558884</v>
+        <v>558829</v>
       </c>
       <c r="R7" t="n">
-        <v>6680516</v>
+        <v>6680608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486567</v>
+        <v>128486876</v>
       </c>
       <c r="B8" t="n">
         <v>92401</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558829</v>
+        <v>558954</v>
       </c>
       <c r="R8" t="n">
-        <v>6680608</v>
+        <v>6680549</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486876</v>
+        <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558954</v>
+        <v>558884</v>
       </c>
       <c r="R9" t="n">
-        <v>6680549</v>
+        <v>6680516</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>92790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R11" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>92790</v>
+        <v>86927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R12" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486655</v>
+        <v>128486971</v>
       </c>
       <c r="B15" t="n">
         <v>92790</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558858</v>
+        <v>558970</v>
       </c>
       <c r="R15" t="n">
-        <v>6680578</v>
+        <v>6680596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486971</v>
+        <v>128486655</v>
       </c>
       <c r="B16" t="n">
         <v>92790</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558970</v>
+        <v>558858</v>
       </c>
       <c r="R16" t="n">
-        <v>6680596</v>
+        <v>6680578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128486478</v>
+        <v>128486938</v>
       </c>
       <c r="B18" t="n">
         <v>92790</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558870</v>
+        <v>558925</v>
       </c>
       <c r="R18" t="n">
-        <v>6680544</v>
+        <v>6680676</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128486938</v>
+        <v>128486478</v>
       </c>
       <c r="B19" t="n">
         <v>92790</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558925</v>
+        <v>558870</v>
       </c>
       <c r="R19" t="n">
-        <v>6680676</v>
+        <v>6680544</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486567</v>
+        <v>128486876</v>
       </c>
       <c r="B7" t="n">
         <v>92401</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558829</v>
+        <v>558954</v>
       </c>
       <c r="R7" t="n">
-        <v>6680608</v>
+        <v>6680549</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486876</v>
+        <v>128486567</v>
       </c>
       <c r="B8" t="n">
         <v>92401</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558954</v>
+        <v>558829</v>
       </c>
       <c r="R8" t="n">
-        <v>6680549</v>
+        <v>6680608</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B11" t="n">
-        <v>92790</v>
+        <v>86927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R11" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B12" t="n">
-        <v>86927</v>
+        <v>92790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R12" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R2" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486559</v>
+        <v>128486359</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558846</v>
+        <v>558865</v>
       </c>
       <c r="R3" t="n">
-        <v>6680607</v>
+        <v>6680514</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486465</v>
+        <v>128486559</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558900</v>
+        <v>558846</v>
       </c>
       <c r="R4" t="n">
-        <v>6680527</v>
+        <v>6680607</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486876</v>
+        <v>128486567</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558954</v>
+        <v>558829</v>
       </c>
       <c r="R7" t="n">
-        <v>6680549</v>
+        <v>6680608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486567</v>
+        <v>128486876</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558829</v>
+        <v>558954</v>
       </c>
       <c r="R8" t="n">
-        <v>6680608</v>
+        <v>6680549</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1357,7 +1357,7 @@
         <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486418</v>
+        <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>92791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558889</v>
+        <v>558913</v>
       </c>
       <c r="R11" t="n">
-        <v>6680512</v>
+        <v>6680658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486924</v>
+        <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>92790</v>
+        <v>86927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558913</v>
+        <v>558889</v>
       </c>
       <c r="R12" t="n">
-        <v>6680658</v>
+        <v>6680512</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486310</v>
+        <v>128486655</v>
       </c>
       <c r="B14" t="n">
-        <v>92768</v>
+        <v>92791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558879</v>
+        <v>558858</v>
       </c>
       <c r="R14" t="n">
-        <v>6680448</v>
+        <v>6680578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1939,7 +1939,7 @@
         <v>128486971</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486655</v>
+        <v>128486310</v>
       </c>
       <c r="B16" t="n">
-        <v>92790</v>
+        <v>92769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558858</v>
+        <v>558879</v>
       </c>
       <c r="R16" t="n">
-        <v>6680578</v>
+        <v>6680448</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128486938</v>
+        <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558925</v>
+        <v>558870</v>
       </c>
       <c r="R18" t="n">
-        <v>6680676</v>
+        <v>6680544</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128486478</v>
+        <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558870</v>
+        <v>558925</v>
       </c>
       <c r="R19" t="n">
-        <v>6680544</v>
+        <v>6680676</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128486465</v>
+        <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558900</v>
+        <v>558865</v>
       </c>
       <c r="R2" t="n">
-        <v>6680527</v>
+        <v>6680514</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486359</v>
+        <v>128486465</v>
       </c>
       <c r="B3" t="n">
-        <v>92759</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558865</v>
+        <v>558900</v>
       </c>
       <c r="R3" t="n">
-        <v>6680514</v>
+        <v>6680527</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>128486559</v>
       </c>
       <c r="B4" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486567</v>
+        <v>128486876</v>
       </c>
       <c r="B7" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558829</v>
+        <v>558954</v>
       </c>
       <c r="R7" t="n">
-        <v>6680608</v>
+        <v>6680549</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486876</v>
+        <v>128486567</v>
       </c>
       <c r="B8" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558954</v>
+        <v>558829</v>
       </c>
       <c r="R8" t="n">
-        <v>6680549</v>
+        <v>6680608</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1357,7 +1357,7 @@
         <v>128486429</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486655</v>
+        <v>128486310</v>
       </c>
       <c r="B14" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558858</v>
+        <v>558879</v>
       </c>
       <c r="R14" t="n">
-        <v>6680578</v>
+        <v>6680448</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486971</v>
+        <v>128486655</v>
       </c>
       <c r="B15" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558970</v>
+        <v>558858</v>
       </c>
       <c r="R15" t="n">
-        <v>6680596</v>
+        <v>6680578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486310</v>
+        <v>128486971</v>
       </c>
       <c r="B16" t="n">
-        <v>92769</v>
+        <v>92818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558879</v>
+        <v>558970</v>
       </c>
       <c r="R16" t="n">
-        <v>6680448</v>
+        <v>6680596</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2516,6 +2516,200 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128842605</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86756</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>558917</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6680640</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128842569</v>
+      </c>
+      <c r="B22" t="n">
+        <v>88750</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558940</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6680626</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92786</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486465</v>
+        <v>128486559</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558900</v>
+        <v>558846</v>
       </c>
       <c r="R3" t="n">
-        <v>6680527</v>
+        <v>6680607</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486559</v>
+        <v>128486465</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558846</v>
+        <v>558900</v>
       </c>
       <c r="R4" t="n">
-        <v>6680607</v>
+        <v>6680527</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>128486263</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128486823</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486876</v>
+        <v>128486429</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558954</v>
+        <v>558884</v>
       </c>
       <c r="R7" t="n">
-        <v>6680549</v>
+        <v>6680516</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
         <v>128486567</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486429</v>
+        <v>128486876</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558884</v>
+        <v>558954</v>
       </c>
       <c r="R9" t="n">
-        <v>6680516</v>
+        <v>6680549</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>128486873</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128486924</v>
       </c>
       <c r="B11" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128486418</v>
       </c>
       <c r="B12" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128486630</v>
       </c>
       <c r="B13" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486310</v>
+        <v>128486655</v>
       </c>
       <c r="B14" t="n">
-        <v>92796</v>
+        <v>92823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558879</v>
+        <v>558858</v>
       </c>
       <c r="R14" t="n">
-        <v>6680448</v>
+        <v>6680578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486655</v>
+        <v>128486971</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558858</v>
+        <v>558970</v>
       </c>
       <c r="R15" t="n">
-        <v>6680578</v>
+        <v>6680596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486971</v>
+        <v>128486310</v>
       </c>
       <c r="B16" t="n">
-        <v>92818</v>
+        <v>92801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558970</v>
+        <v>558879</v>
       </c>
       <c r="R16" t="n">
-        <v>6680596</v>
+        <v>6680448</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2133,7 +2133,7 @@
         <v>128486727</v>
       </c>
       <c r="B17" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128486478</v>
       </c>
       <c r="B18" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128486938</v>
       </c>
       <c r="B19" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128486598</v>
       </c>
       <c r="B20" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88771</v>
+        <v>88774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88774</v>
+        <v>88777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86795</v>
+        <v>86796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88790</v>
+        <v>88791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
         <v>128842605</v>
       </c>
       <c r="B21" t="n">
-        <v>86796</v>
+        <v>86799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128842569</v>
       </c>
       <c r="B22" t="n">
-        <v>88791</v>
+        <v>88794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2710,6 +2710,103 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128842720</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87123</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>558828</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6680607</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2715,7 +2715,7 @@
         <v>128842720</v>
       </c>
       <c r="B23" t="n">
-        <v>87123</v>
+        <v>87124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2715,7 +2715,7 @@
         <v>128842720</v>
       </c>
       <c r="B23" t="n">
-        <v>87124</v>
+        <v>87141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -2715,7 +2715,7 @@
         <v>128842720</v>
       </c>
       <c r="B23" t="n">
-        <v>87157</v>
+        <v>87244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>128486359</v>
       </c>
       <c r="B2" t="n">
-        <v>92808</v>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128486559</v>
+        <v>128842720</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>87412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>3624</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensboberget, Rensboberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558846</v>
+        <v>558828</v>
       </c>
       <c r="R3" t="n">
         <v>6680607</v>
@@ -837,12 +836,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,6 +850,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486465</v>
+        <v>128842605</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>87146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558900</v>
+        <v>558917</v>
       </c>
       <c r="R4" t="n">
-        <v>6680527</v>
+        <v>6680640</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486263</v>
+        <v>128486310</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558915</v>
+        <v>558879</v>
       </c>
       <c r="R5" t="n">
-        <v>6680423</v>
+        <v>6680448</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128486823</v>
+        <v>128842627</v>
       </c>
       <c r="B6" t="n">
-        <v>92451</v>
+        <v>89138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>4404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558883</v>
+        <v>558915</v>
       </c>
       <c r="R6" t="n">
-        <v>6680540</v>
+        <v>6680638</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128486567</v>
+        <v>128842569</v>
       </c>
       <c r="B7" t="n">
-        <v>92451</v>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558829</v>
+        <v>558940</v>
       </c>
       <c r="R7" t="n">
-        <v>6680608</v>
+        <v>6680626</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486876</v>
+        <v>128486465</v>
       </c>
       <c r="B8" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558954</v>
+        <v>558900</v>
       </c>
       <c r="R8" t="n">
-        <v>6680549</v>
+        <v>6680527</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486429</v>
+        <v>128486567</v>
       </c>
       <c r="B9" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558884</v>
+        <v>558829</v>
       </c>
       <c r="R9" t="n">
-        <v>6680516</v>
+        <v>6680608</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128486873</v>
+        <v>128486823</v>
       </c>
       <c r="B10" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558945</v>
+        <v>558883</v>
       </c>
       <c r="R10" t="n">
-        <v>6680547</v>
+        <v>6680540</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128486924</v>
+        <v>128486876</v>
       </c>
       <c r="B11" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558913</v>
+        <v>558954</v>
       </c>
       <c r="R11" t="n">
-        <v>6680658</v>
+        <v>6680549</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128486418</v>
+        <v>128486968</v>
       </c>
       <c r="B12" t="n">
-        <v>86970</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558889</v>
+        <v>558973</v>
       </c>
       <c r="R12" t="n">
-        <v>6680512</v>
+        <v>6680612</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128486630</v>
+        <v>128486727</v>
       </c>
       <c r="B13" t="n">
-        <v>92842</v>
+        <v>91435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558850</v>
+        <v>558855</v>
       </c>
       <c r="R13" t="n">
-        <v>6680597</v>
+        <v>6680550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486310</v>
+        <v>128486263</v>
       </c>
       <c r="B14" t="n">
-        <v>92818</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558879</v>
+        <v>558915</v>
       </c>
       <c r="R14" t="n">
-        <v>6680448</v>
+        <v>6680423</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486655</v>
+        <v>128486429</v>
       </c>
       <c r="B15" t="n">
-        <v>92842</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558858</v>
+        <v>558884</v>
       </c>
       <c r="R15" t="n">
-        <v>6680578</v>
+        <v>6680516</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2033,14 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486971</v>
+        <v>128486478</v>
       </c>
       <c r="B16" t="n">
-        <v>92842</v>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558970</v>
+        <v>558870</v>
       </c>
       <c r="R16" t="n">
-        <v>6680596</v>
+        <v>6680544</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128486727</v>
+        <v>128486559</v>
       </c>
       <c r="B17" t="n">
-        <v>91050</v>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558855</v>
+        <v>558846</v>
       </c>
       <c r="R17" t="n">
-        <v>6680550</v>
+        <v>6680607</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2227,14 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128486478</v>
+        <v>128486630</v>
       </c>
       <c r="B18" t="n">
-        <v>92842</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558870</v>
+        <v>558850</v>
       </c>
       <c r="R18" t="n">
-        <v>6680544</v>
+        <v>6680597</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2324,14 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128486938</v>
+        <v>128486655</v>
       </c>
       <c r="B19" t="n">
-        <v>92842</v>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558925</v>
+        <v>558858</v>
       </c>
       <c r="R19" t="n">
-        <v>6680676</v>
+        <v>6680578</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128486598</v>
+        <v>128486873</v>
       </c>
       <c r="B20" t="n">
-        <v>86970</v>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558837</v>
+        <v>558945</v>
       </c>
       <c r="R20" t="n">
-        <v>6680592</v>
+        <v>6680547</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128842605</v>
+        <v>128486924</v>
       </c>
       <c r="B21" t="n">
-        <v>86799</v>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558917</v>
+        <v>558913</v>
       </c>
       <c r="R21" t="n">
-        <v>6680640</v>
+        <v>6680658</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128842569</v>
+        <v>128486938</v>
       </c>
       <c r="B22" t="n">
-        <v>88794</v>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558940</v>
+        <v>558925</v>
       </c>
       <c r="R22" t="n">
-        <v>6680626</v>
+        <v>6680676</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,44 +2712,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128842720</v>
+        <v>128486971</v>
       </c>
       <c r="B23" t="n">
-        <v>87244</v>
+        <v>93233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3624</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rensboberget, Rensboberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558828</v>
+        <v>558970</v>
       </c>
       <c r="R23" t="n">
-        <v>6680607</v>
+        <v>6680596</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2776,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2790,7 +2791,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2806,6 +2806,200 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128486418</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>558889</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6680512</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128486598</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rensboberget, Rensboberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>558837</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6680592</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38724-2025 artfynd.xlsx
+++ b/artfynd/A 38724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486359</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842605</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486465</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486876</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486968</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486727</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486263</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486429</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486478</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486559</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486630</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486655</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486924</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486938</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486971</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486418</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,8 +3120,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>